--- a/EntraLab_BulkCreateUsers.xlsx
+++ b/EntraLab_BulkCreateUsers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rythem\Documents\GitHub\EntraID\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{23943916-B948-4B8E-8C97-9BCB24C1728F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{74280E4F-1520-4A89-BD05-B0C81F9E5FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CECCB8CA-2CEB-44B9-946B-547FD8387247}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{CECCB8CA-2CEB-44B9-946B-547FD8387247}"/>
   </bookViews>
   <sheets>
     <sheet name="EntraLab_BulkCreateUsers" sheetId="1" r:id="rId1"/>
@@ -88,9 +88,6 @@
     <t>Rivera</t>
   </si>
   <si>
-    <t>Global Administrator</t>
-  </si>
-  <si>
     <t>IT-Admins</t>
   </si>
   <si>
@@ -680,6 +677,9 @@
   </si>
   <si>
     <t>Created Manually</t>
+  </si>
+  <si>
+    <t>isus</t>
   </si>
 </sst>
 </file>
@@ -1545,6 +1545,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1820EDEC-0829-4F4A-8EFC-232A1F845CD0}">
   <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="7" max="7" width="18.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1619,1139 +1623,1139 @@
         <v>21</v>
       </c>
       <c r="G2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>28</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
       </c>
       <c r="O2">
         <v>98101</v>
       </c>
       <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
         <v>30</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
         <v>35</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>36</v>
       </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
       <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>24</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>27</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>28</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
       </c>
       <c r="O3">
         <v>98101</v>
       </c>
       <c r="P3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" t="s">
         <v>38</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>42</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
         <v>43</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>44</v>
       </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
       <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
         <v>23</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>24</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>25</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>26</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>27</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
       </c>
       <c r="O4">
         <v>98101</v>
       </c>
       <c r="P4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q4" t="s">
         <v>46</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
         <v>48</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>49</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" t="s">
         <v>51</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>52</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>53</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
         <v>54</v>
       </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
         <v>55</v>
       </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" t="s">
-        <v>56</v>
-      </c>
       <c r="N5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O5">
         <v>98102</v>
       </c>
       <c r="P5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5" t="s">
         <v>57</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
         <v>59</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" t="s">
         <v>62</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>63</v>
       </c>
-      <c r="G6" t="s">
-        <v>64</v>
-      </c>
       <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
         <v>54</v>
       </c>
-      <c r="I6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
         <v>55</v>
       </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" t="s">
-        <v>56</v>
-      </c>
       <c r="N6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O6">
         <v>98102</v>
       </c>
       <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s">
         <v>65</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
         <v>67</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" t="s">
         <v>70</v>
       </c>
-      <c r="G7" t="s">
-        <v>71</v>
-      </c>
       <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
         <v>54</v>
       </c>
-      <c r="I7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
         <v>55</v>
       </c>
-      <c r="K7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" t="s">
-        <v>56</v>
-      </c>
       <c r="N7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O7">
         <v>98102</v>
       </c>
       <c r="P7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q7" t="s">
         <v>72</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
         <v>74</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" t="s">
         <v>77</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>78</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>79</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
         <v>80</v>
       </c>
-      <c r="I8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
         <v>81</v>
       </c>
-      <c r="K8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" t="s">
-        <v>82</v>
-      </c>
       <c r="N8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O8">
         <v>98103</v>
       </c>
       <c r="P8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q8" t="s">
         <v>83</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
         <v>85</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>86</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" t="s">
         <v>88</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>89</v>
       </c>
-      <c r="G9" t="s">
-        <v>90</v>
-      </c>
       <c r="H9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" t="s">
         <v>80</v>
       </c>
-      <c r="I9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" t="s">
         <v>81</v>
       </c>
-      <c r="K9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" t="s">
-        <v>82</v>
-      </c>
       <c r="N9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O9">
         <v>98103</v>
       </c>
       <c r="P9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q9" t="s">
         <v>91</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" t="s">
         <v>93</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>94</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
         <v>96</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>97</v>
       </c>
-      <c r="G10" t="s">
-        <v>98</v>
-      </c>
       <c r="H10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
         <v>80</v>
       </c>
-      <c r="I10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" t="s">
         <v>81</v>
       </c>
-      <c r="K10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" t="s">
-        <v>82</v>
-      </c>
       <c r="N10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O10">
         <v>98103</v>
       </c>
       <c r="P10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q10" t="s">
         <v>99</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" t="s">
         <v>101</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>102</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" t="s">
         <v>104</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>105</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>106</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
         <v>107</v>
       </c>
-      <c r="I11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
         <v>108</v>
       </c>
-      <c r="K11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" t="s">
-        <v>109</v>
-      </c>
       <c r="N11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O11">
         <v>98104</v>
       </c>
       <c r="P11" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q11" t="s">
         <v>110</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" t="s">
         <v>112</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>113</v>
-      </c>
-      <c r="C12" t="s">
-        <v>114</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" t="s">
         <v>115</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>116</v>
       </c>
-      <c r="G12" t="s">
-        <v>117</v>
-      </c>
       <c r="H12" t="s">
+        <v>106</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
         <v>107</v>
       </c>
-      <c r="I12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" t="s">
         <v>108</v>
       </c>
-      <c r="K12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" t="s">
-        <v>109</v>
-      </c>
       <c r="N12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12">
         <v>98104</v>
       </c>
       <c r="P12" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q12" t="s">
         <v>118</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" t="s">
         <v>120</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>121</v>
-      </c>
-      <c r="C13" t="s">
-        <v>122</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" t="s">
         <v>123</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>124</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>125</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
         <v>126</v>
       </c>
-      <c r="I13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
         <v>127</v>
       </c>
-      <c r="K13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" t="s">
-        <v>128</v>
-      </c>
       <c r="N13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O13">
         <v>98105</v>
       </c>
       <c r="P13" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q13" t="s">
         <v>129</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" t="s">
         <v>131</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>132</v>
-      </c>
-      <c r="C14" t="s">
-        <v>133</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14" t="s">
         <v>134</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>135</v>
       </c>
-      <c r="G14" t="s">
-        <v>136</v>
-      </c>
       <c r="H14" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
         <v>126</v>
       </c>
-      <c r="I14" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
         <v>127</v>
       </c>
-      <c r="K14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" t="s">
-        <v>128</v>
-      </c>
       <c r="N14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O14">
         <v>98105</v>
       </c>
       <c r="P14" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q14" t="s">
         <v>137</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" t="s">
         <v>139</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>140</v>
-      </c>
-      <c r="C15" t="s">
-        <v>141</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
+        <v>141</v>
+      </c>
+      <c r="F15" t="s">
         <v>142</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>143</v>
       </c>
-      <c r="G15" t="s">
-        <v>144</v>
-      </c>
       <c r="H15" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
         <v>126</v>
       </c>
-      <c r="I15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
         <v>127</v>
       </c>
-      <c r="K15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" t="s">
-        <v>128</v>
-      </c>
       <c r="N15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O15">
         <v>98105</v>
       </c>
       <c r="P15" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q15" t="s">
         <v>145</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" t="s">
         <v>147</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>148</v>
-      </c>
-      <c r="C16" t="s">
-        <v>149</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
+        <v>149</v>
+      </c>
+      <c r="F16" t="s">
         <v>150</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>151</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>152</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" t="s">
         <v>153</v>
       </c>
-      <c r="I16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
         <v>154</v>
       </c>
-      <c r="K16" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" t="s">
-        <v>155</v>
-      </c>
       <c r="N16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O16">
         <v>98106</v>
       </c>
       <c r="P16" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q16" t="s">
         <v>156</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" t="s">
         <v>158</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>159</v>
-      </c>
-      <c r="C17" t="s">
-        <v>160</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" t="s">
         <v>161</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>162</v>
       </c>
-      <c r="G17" t="s">
-        <v>163</v>
-      </c>
       <c r="H17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" t="s">
         <v>153</v>
       </c>
-      <c r="I17" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" t="s">
         <v>154</v>
       </c>
-      <c r="K17" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" t="s">
-        <v>155</v>
-      </c>
       <c r="N17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O17">
         <v>98106</v>
       </c>
       <c r="P17" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q17" t="s">
         <v>164</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" t="s">
         <v>166</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>167</v>
-      </c>
-      <c r="C18" t="s">
-        <v>168</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
+        <v>168</v>
+      </c>
+      <c r="F18" t="s">
         <v>169</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>170</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>171</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" t="s">
         <v>172</v>
       </c>
-      <c r="I18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" t="s">
         <v>173</v>
       </c>
-      <c r="K18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" t="s">
-        <v>174</v>
-      </c>
       <c r="N18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O18">
         <v>98107</v>
       </c>
       <c r="P18" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q18" t="s">
         <v>175</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" t="s">
         <v>177</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>178</v>
-      </c>
-      <c r="C19" t="s">
-        <v>179</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" t="s">
         <v>180</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>181</v>
       </c>
-      <c r="G19" t="s">
-        <v>182</v>
-      </c>
       <c r="H19" t="s">
+        <v>171</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
         <v>172</v>
       </c>
-      <c r="I19" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
         <v>173</v>
       </c>
-      <c r="K19" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" t="s">
-        <v>174</v>
-      </c>
       <c r="N19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O19">
         <v>98107</v>
       </c>
       <c r="P19" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q19" t="s">
         <v>183</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" t="s">
         <v>185</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>186</v>
-      </c>
-      <c r="C20" t="s">
-        <v>187</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" t="s">
         <v>188</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>189</v>
       </c>
-      <c r="G20" t="s">
-        <v>190</v>
-      </c>
       <c r="H20" t="s">
+        <v>171</v>
+      </c>
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" t="s">
         <v>172</v>
       </c>
-      <c r="I20" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" t="s">
         <v>173</v>
       </c>
-      <c r="K20" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" t="s">
-        <v>174</v>
-      </c>
       <c r="N20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O20">
         <v>98107</v>
       </c>
       <c r="P20" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q20" t="s">
         <v>191</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B21" t="s">
         <v>193</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>194</v>
-      </c>
-      <c r="C21" t="s">
-        <v>195</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F21" t="s">
         <v>196</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>197</v>
       </c>
-      <c r="G21" t="s">
-        <v>198</v>
-      </c>
       <c r="H21" t="s">
+        <v>171</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" t="s">
         <v>172</v>
       </c>
-      <c r="I21" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" t="s">
         <v>173</v>
       </c>
-      <c r="K21" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" t="s">
-        <v>174</v>
-      </c>
       <c r="N21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O21">
         <v>98107</v>
       </c>
       <c r="P21" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q21" t="s">
         <v>199</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" t="s">
         <v>201</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" t="s">
         <v>205</v>
       </c>
-      <c r="B25" t="s">
-        <v>206</v>
-      </c>
       <c r="D25" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B26" t="s">
         <v>207</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>209</v>
+      </c>
+      <c r="B27" t="s">
         <v>210</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" t="s">
         <v>213</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>215</v>
+      </c>
+      <c r="B29" t="s">
         <v>216</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
